--- a/resources/HR Docs/11 - Employee Compensation/5 - CTC Calculator.xlsx
+++ b/resources/HR Docs/11 - Employee Compensation/5 - CTC Calculator.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Vikky\Vikky\resources\HR Docs\11 - Employee Compensation\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C8A8856-9243-4AE0-A687-92649B25D13B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="144" windowWidth="22980" windowHeight="8760"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -12,12 +18,23 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$E$36</definedName>
   </definedNames>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="34">
   <si>
     <t>Name:</t>
   </si>
@@ -32,9 +49,6 @@
   </si>
   <si>
     <t>Monthly</t>
-  </si>
-  <si>
-    <t>Annaual</t>
   </si>
   <si>
     <t>CTC</t>
@@ -127,12 +141,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -510,46 +524,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -614,61 +593,94 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="2" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -680,14 +692,17 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -725,7 +740,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -797,7 +812,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -970,9 +985,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E36"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.44140625" customWidth="1"/>
     <col min="2" max="2" width="23.44140625" bestFit="1" customWidth="1"/>
@@ -987,430 +1002,430 @@
     <col min="13" max="13" width="9.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15" thickBot="1">
-      <c r="A1" s="56"/>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-    </row>
-    <row r="2" spans="1:5" ht="15" thickBot="1">
-      <c r="A2" s="57"/>
-      <c r="B2" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C2" s="10"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="57"/>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="57"/>
-      <c r="B3" s="53" t="s">
+    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="31"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+    </row>
+    <row r="2" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="32"/>
+      <c r="B2" s="41" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" s="42"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="32"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="32"/>
+      <c r="B3" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="47" t="s">
+      <c r="C3" s="44" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="45"/>
+      <c r="E3" s="32"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="32"/>
+      <c r="B4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="46" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="42"/>
-      <c r="E3" s="57"/>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="57"/>
-      <c r="B4" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="48" t="s">
+      <c r="D4" s="47"/>
+      <c r="E4" s="32"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="32"/>
+      <c r="B5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="43"/>
-      <c r="E4" s="57"/>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="57"/>
-      <c r="B5" s="54" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="48" t="s">
+      <c r="D5" s="47"/>
+      <c r="E5" s="32"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="32"/>
+      <c r="B6" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D5" s="43"/>
-      <c r="E5" s="57"/>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="57"/>
-      <c r="B6" s="54" t="s">
+      <c r="C6" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="C6" s="48" t="s">
+      <c r="D6" s="47"/>
+      <c r="E6" s="32"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="32"/>
+      <c r="B7" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="54" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="55"/>
+      <c r="E7" s="32"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="32"/>
+      <c r="B8" s="30"/>
+      <c r="C8" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="32"/>
+    </row>
+    <row r="9" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="32"/>
+      <c r="B9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="28">
+        <v>50000</v>
+      </c>
+      <c r="D9" s="26">
+        <f>C9*12</f>
+        <v>600000</v>
+      </c>
+      <c r="E9" s="32"/>
+    </row>
+    <row r="10" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="32"/>
+      <c r="B10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="50">
+        <v>0.12</v>
+      </c>
+      <c r="D10" s="51"/>
+      <c r="E10" s="32"/>
+    </row>
+    <row r="11" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="32"/>
+      <c r="B11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="52" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="53"/>
+      <c r="E11" s="32"/>
+    </row>
+    <row r="12" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="32"/>
+      <c r="B12" s="33"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="32"/>
+    </row>
+    <row r="13" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="32"/>
+      <c r="B13" s="56" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="43"/>
-      <c r="E6" s="57"/>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="57"/>
-      <c r="B7" s="54" t="s">
-        <v>3</v>
-      </c>
-      <c r="C7" s="49" t="s">
+      <c r="C13" s="52"/>
+      <c r="D13" s="53"/>
+      <c r="E13" s="32"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="32"/>
+      <c r="B14" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="D7" s="44"/>
-      <c r="E7" s="57"/>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="57"/>
-      <c r="B8" s="55"/>
-      <c r="C8" s="50" t="s">
-        <v>4</v>
-      </c>
-      <c r="D8" s="45" t="s">
-        <v>5</v>
-      </c>
-      <c r="E8" s="57"/>
-    </row>
-    <row r="9" spans="1:5" ht="15" thickBot="1">
-      <c r="A9" s="57"/>
-      <c r="B9" s="54" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" s="51">
-        <v>18000</v>
-      </c>
-      <c r="D9" s="46">
-        <f>C9*12</f>
-        <v>216000</v>
-      </c>
-      <c r="E9" s="57"/>
-    </row>
-    <row r="10" spans="1:5" ht="15" thickBot="1">
-      <c r="A10" s="57"/>
-      <c r="B10" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="52">
-        <v>0.12</v>
-      </c>
-      <c r="D10" s="38"/>
-      <c r="E10" s="57"/>
-    </row>
-    <row r="11" spans="1:5" ht="15" thickBot="1">
-      <c r="A11" s="57"/>
-      <c r="B11" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="41" t="s">
-        <v>24</v>
-      </c>
-      <c r="D11" s="40"/>
-      <c r="E11" s="57"/>
-    </row>
-    <row r="12" spans="1:5" ht="15" thickBot="1">
-      <c r="A12" s="57"/>
-      <c r="B12" s="58"/>
-      <c r="C12" s="58"/>
-      <c r="D12" s="58"/>
-      <c r="E12" s="57"/>
-    </row>
-    <row r="13" spans="1:5" ht="15" thickBot="1">
-      <c r="A13" s="57"/>
-      <c r="B13" s="39" t="s">
-        <v>33</v>
-      </c>
-      <c r="C13" s="41"/>
-      <c r="D13" s="40"/>
-      <c r="E13" s="57"/>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="57"/>
-      <c r="B14" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14" s="4"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="57"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" thickBot="1">
-      <c r="A15" s="57"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="57"/>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="57"/>
-      <c r="B16" s="12" t="str">
+      <c r="C14" s="36"/>
+      <c r="D14" s="37"/>
+      <c r="E14" s="32"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="32"/>
+      <c r="B15" s="38"/>
+      <c r="C15" s="39"/>
+      <c r="D15" s="40"/>
+      <c r="E15" s="32"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="32"/>
+      <c r="B16" s="2" t="str">
         <f>C3</f>
         <v>Preet Sonpal</v>
       </c>
-      <c r="C16" s="13" t="str">
+      <c r="C16" s="48" t="str">
         <f>CONCATENATE("Joined On: ",C6)</f>
         <v>Joined On: 18th Aug, 2020</v>
       </c>
-      <c r="D16" s="13"/>
-      <c r="E16" s="57"/>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="57"/>
-      <c r="B17" s="14" t="str">
+      <c r="D16" s="48"/>
+      <c r="E16" s="32"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="32"/>
+      <c r="B17" s="3" t="str">
         <f>C4</f>
         <v>Marketing Manager</v>
       </c>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="57"/>
-    </row>
-    <row r="18" spans="1:5" ht="15" thickBot="1">
-      <c r="A18" s="57"/>
-      <c r="B18" s="14" t="str">
+      <c r="C17" s="49"/>
+      <c r="D17" s="49"/>
+      <c r="E17" s="32"/>
+    </row>
+    <row r="18" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="32"/>
+      <c r="B18" s="3" t="str">
         <f>C5</f>
         <v>Mumbai</v>
       </c>
-      <c r="C18" s="15"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="57"/>
-    </row>
-    <row r="19" spans="1:5" ht="15" thickBot="1">
-      <c r="A19" s="57"/>
-      <c r="B19" s="16" t="s">
+      <c r="C18" s="49"/>
+      <c r="D18" s="49"/>
+      <c r="E18" s="32"/>
+    </row>
+    <row r="19" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="32"/>
+      <c r="B19" s="34" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="34"/>
+      <c r="D19" s="34"/>
+      <c r="E19" s="32"/>
+    </row>
+    <row r="20" spans="1:5" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="32"/>
+      <c r="B20" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="16"/>
-      <c r="D19" s="16"/>
-      <c r="E19" s="57"/>
-    </row>
-    <row r="20" spans="1:5" ht="15" thickBot="1">
-      <c r="A20" s="57"/>
-      <c r="B20" s="17" t="s">
+      <c r="C20" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D20" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C20" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="D20" s="18" t="s">
+      <c r="E20" s="32"/>
+    </row>
+    <row r="21" spans="1:5" ht="15" x14ac:dyDescent="0.3">
+      <c r="A21" s="32"/>
+      <c r="B21" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E20" s="57"/>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="57"/>
-      <c r="B21" s="19" t="s">
+      <c r="C21" s="7">
+        <f>IF(C7="Yes",C9*50%,C9*40%)</f>
+        <v>25000</v>
+      </c>
+      <c r="D21" s="8">
+        <f>C21*12</f>
+        <v>300000</v>
+      </c>
+      <c r="E21" s="32"/>
+    </row>
+    <row r="22" spans="1:5" ht="15" x14ac:dyDescent="0.3">
+      <c r="A22" s="32"/>
+      <c r="B22" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C21" s="20">
-        <f>IF(C7="Yes",C9*50%,C9*40%)</f>
-        <v>9000</v>
-      </c>
-      <c r="D21" s="21">
-        <f>C21*12</f>
-        <v>108000</v>
-      </c>
-      <c r="E21" s="57"/>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="57"/>
-      <c r="B22" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="23">
+      <c r="C22" s="10">
         <f>C21*50%</f>
-        <v>4500</v>
-      </c>
-      <c r="D22" s="24">
+        <v>12500</v>
+      </c>
+      <c r="D22" s="11">
         <f t="shared" ref="D22:D24" si="0">C22*12</f>
-        <v>54000</v>
-      </c>
-      <c r="E22" s="57"/>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="57"/>
-      <c r="B23" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="C23" s="23">
+        <v>150000</v>
+      </c>
+      <c r="E22" s="32"/>
+    </row>
+    <row r="23" spans="1:5" ht="15" x14ac:dyDescent="0.3">
+      <c r="A23" s="32"/>
+      <c r="B23" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C23" s="10">
         <v>1500</v>
       </c>
-      <c r="D23" s="24">
+      <c r="D23" s="11">
         <f t="shared" si="0"/>
         <v>18000</v>
       </c>
-      <c r="E23" s="57"/>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="57"/>
-      <c r="B24" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="C24" s="23">
+      <c r="E23" s="32"/>
+    </row>
+    <row r="24" spans="1:5" ht="15" x14ac:dyDescent="0.3">
+      <c r="A24" s="32"/>
+      <c r="B24" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24" s="10">
         <v>0</v>
       </c>
-      <c r="D24" s="24">
+      <c r="D24" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E24" s="57"/>
-    </row>
-    <row r="25" spans="1:5" ht="15" thickBot="1">
-      <c r="A25" s="57"/>
-      <c r="B25" s="35" t="s">
+      <c r="E24" s="32"/>
+    </row>
+    <row r="25" spans="1:5" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="32"/>
+      <c r="B25" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="15">
+        <f>C9-SUM(C21:C23)</f>
+        <v>11000</v>
+      </c>
+      <c r="D25" s="15">
+        <f>D9-SUM(D21:D23)</f>
+        <v>132000</v>
+      </c>
+      <c r="E25" s="32"/>
+    </row>
+    <row r="26" spans="1:5" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="32"/>
+      <c r="B26" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="C25" s="28">
-        <f>C9-SUM(C21:C23)</f>
-        <v>3000</v>
-      </c>
-      <c r="D25" s="28">
-        <f>D9-SUM(D21:D23)</f>
-        <v>36000</v>
-      </c>
-      <c r="E25" s="57"/>
-    </row>
-    <row r="26" spans="1:5" ht="15" thickBot="1">
-      <c r="A26" s="57"/>
-      <c r="B26" s="36" t="s">
+      <c r="C26" s="24">
+        <f>SUM(C21:C25)</f>
+        <v>50000</v>
+      </c>
+      <c r="D26" s="24">
+        <f>SUM(D21:D25)</f>
+        <v>600000</v>
+      </c>
+      <c r="E26" s="32"/>
+    </row>
+    <row r="27" spans="1:5" ht="15" x14ac:dyDescent="0.3">
+      <c r="A27" s="32"/>
+      <c r="B27" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C26" s="37">
-        <f>SUM(C21:C25)</f>
-        <v>18000</v>
-      </c>
-      <c r="D26" s="37">
-        <f>SUM(D21:D25)</f>
-        <v>216000</v>
-      </c>
-      <c r="E26" s="57"/>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="57"/>
-      <c r="B27" s="19" t="s">
+      <c r="C27" s="7">
+        <f>(C26-C22)*C10</f>
+        <v>4500</v>
+      </c>
+      <c r="D27" s="8">
+        <f t="shared" ref="D27" si="1">C27*12</f>
+        <v>54000</v>
+      </c>
+      <c r="E27" s="32"/>
+    </row>
+    <row r="28" spans="1:5" ht="15" x14ac:dyDescent="0.3">
+      <c r="A28" s="32"/>
+      <c r="B28" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C27" s="20">
-        <f>(C26-C22)*C10</f>
-        <v>1620</v>
-      </c>
-      <c r="D27" s="21">
-        <f t="shared" ref="D27" si="1">C27*12</f>
-        <v>19440</v>
-      </c>
-      <c r="E27" s="57"/>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="57"/>
-      <c r="B28" s="22" t="s">
+      <c r="C28" s="10">
+        <f>IF(C26&lt;20000,IF(C11="Yes",C26*0.75%,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="D28" s="11">
+        <f>C28*12</f>
+        <v>0</v>
+      </c>
+      <c r="E28" s="32"/>
+    </row>
+    <row r="29" spans="1:5" ht="15" x14ac:dyDescent="0.3">
+      <c r="A29" s="32"/>
+      <c r="B29" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C28" s="23">
-        <f>IF(C26&lt;20000,IF(C11="Yes",C26*0.75%,0),0)</f>
-        <v>135</v>
-      </c>
-      <c r="D28" s="24">
-        <f>C28*12</f>
-        <v>1620</v>
-      </c>
-      <c r="E28" s="57"/>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="57"/>
-      <c r="B29" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="C29" s="23">
+      <c r="C29" s="10">
         <v>200</v>
       </c>
-      <c r="D29" s="24">
+      <c r="D29" s="11">
         <f>C29*12+100</f>
         <v>2500</v>
       </c>
-      <c r="E29" s="57"/>
-    </row>
-    <row r="30" spans="1:5" ht="15" thickBot="1">
-      <c r="A30" s="57"/>
-      <c r="B30" s="26" t="s">
+      <c r="E29" s="32"/>
+    </row>
+    <row r="30" spans="1:5" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="32"/>
+      <c r="B30" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" s="15">
+        <v>0</v>
+      </c>
+      <c r="D30" s="17">
+        <v>0</v>
+      </c>
+      <c r="E30" s="32"/>
+    </row>
+    <row r="31" spans="1:5" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="32"/>
+      <c r="B31" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="C30" s="28">
-        <v>0</v>
-      </c>
-      <c r="D30" s="30">
-        <v>0</v>
-      </c>
-      <c r="E30" s="57"/>
-    </row>
-    <row r="31" spans="1:5" ht="15" thickBot="1">
-      <c r="A31" s="57"/>
-      <c r="B31" s="33" t="s">
+      <c r="C31" s="21">
+        <f>C26-C27-C28-C29-C30</f>
+        <v>45300</v>
+      </c>
+      <c r="D31" s="21">
+        <f>D26-D27-D28-D29-D30</f>
+        <v>543500</v>
+      </c>
+      <c r="E31" s="32"/>
+    </row>
+    <row r="32" spans="1:5" ht="15" x14ac:dyDescent="0.3">
+      <c r="A32" s="32"/>
+      <c r="B32" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="C31" s="34">
-        <f>C26-C27-C28-C29-C30</f>
-        <v>16045</v>
-      </c>
-      <c r="D31" s="34">
-        <f>D26-D27-D28-D29-D30</f>
-        <v>192440</v>
-      </c>
-      <c r="E31" s="57"/>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="57"/>
-      <c r="B32" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="C32" s="32"/>
-      <c r="D32" s="20">
+      <c r="C32" s="19"/>
+      <c r="D32" s="7">
         <f>C32*12</f>
         <v>0</v>
       </c>
-      <c r="E32" s="57"/>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="57"/>
-      <c r="B33" s="22" t="s">
+      <c r="E32" s="32"/>
+    </row>
+    <row r="33" spans="1:5" ht="15" x14ac:dyDescent="0.3">
+      <c r="A33" s="32"/>
+      <c r="B33" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C33" s="11">
+        <v>0</v>
+      </c>
+      <c r="D33" s="11">
+        <v>0</v>
+      </c>
+      <c r="E33" s="32"/>
+    </row>
+    <row r="34" spans="1:5" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="32"/>
+      <c r="B34" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C33" s="24">
+      <c r="C34" s="14">
         <v>0</v>
       </c>
-      <c r="D33" s="24">
+      <c r="D34" s="15">
         <v>0</v>
       </c>
-      <c r="E33" s="57"/>
-    </row>
-    <row r="34" spans="1:5" ht="15" thickBot="1">
-      <c r="A34" s="57"/>
-      <c r="B34" s="26" t="s">
+      <c r="E34" s="32"/>
+    </row>
+    <row r="35" spans="1:5" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="32"/>
+      <c r="B35" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C34" s="27">
-        <v>0</v>
-      </c>
-      <c r="D34" s="28">
-        <v>0</v>
-      </c>
-      <c r="E34" s="57"/>
-    </row>
-    <row r="35" spans="1:5" ht="15" thickBot="1">
-      <c r="A35" s="57"/>
-      <c r="B35" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="C35" s="29">
+      <c r="C35" s="16">
         <f>C31+C32+C33+C34</f>
-        <v>16045</v>
-      </c>
-      <c r="D35" s="29">
+        <v>45300</v>
+      </c>
+      <c r="D35" s="16">
         <f>D31+D32+D33+D34</f>
-        <v>192440</v>
-      </c>
-      <c r="E35" s="57"/>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="57"/>
-      <c r="B36" s="57"/>
-      <c r="C36" s="57"/>
-      <c r="D36" s="57"/>
-      <c r="E36" s="57"/>
+        <v>543500</v>
+      </c>
+      <c r="E35" s="32"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" s="32"/>
+      <c r="B36" s="32"/>
+      <c r="C36" s="32"/>
+      <c r="D36" s="32"/>
+      <c r="E36" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -1430,7 +1445,7 @@
     <mergeCell ref="B13:D13"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C7 C11:C12">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C7 C11:C12" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Yes, No"</formula1>
     </dataValidation>
   </dataValidations>
